--- a/data/trans_dic/P25C$smedicoempresa_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,65</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,66</t>
+          <t>0,06; 0,62</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3071</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2302</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1879</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2083</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1333</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1606</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6523</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2312</t>
+          <t>0; 1957</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2522</t>
+          <t>0; 2573</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6182</t>
+          <t>0; 6135</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1102</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6943</t>
+          <t>0; 6416</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1264</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 978</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1190</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2503</t>
+          <t>0; 2827</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3418</t>
+          <t>0; 2852</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6642</t>
+          <t>0; 7332</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2565</t>
+          <t>0; 1917</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>500; 7838</t>
+          <t>701; 7321</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$smedicoempresa_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Edad-trans_dic.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,09; 1,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,62</t>
+          <t>0,06; 0,66</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>0; 1860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2573</t>
+          <t>0; 2099</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6135</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6416</t>
+          <t>0; 5795</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2827</t>
+          <t>0; 2863</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2852</t>
+          <t>0; 2849</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 7332</t>
+          <t>573; 7275</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 1917</t>
+          <t>0; 1844</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>701; 7321</t>
+          <t>627; 6792</t>
         </is>
       </c>
     </row>
